--- a/data/raw/Azadpur Cherry.xlsx
+++ b/data/raw/Azadpur Cherry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\Price_forecasting_project\Agricultural-Price-Intelligence\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5881C3A-4F9F-4306-B410-3E4F856C81E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F45517B-9A40-4B43-9817-92EF9FA06E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1B1FD34-CC1A-4FE3-A802-618D65623F84}"/>
   </bookViews>
@@ -36669,7 +36669,7 @@
         <v>2</v>
       </c>
       <c r="F1250" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1250">
         <v>40</v>
@@ -36727,7 +36727,7 @@
         <v>2</v>
       </c>
       <c r="F1252" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1252">
         <v>80</v>
@@ -36756,7 +36756,7 @@
         <v>2</v>
       </c>
       <c r="F1253" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1253">
         <v>30</v>
@@ -36814,7 +36814,7 @@
         <v>2</v>
       </c>
       <c r="F1255" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1255">
         <v>90</v>
@@ -36843,7 +36843,7 @@
         <v>2</v>
       </c>
       <c r="F1256" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1256">
         <v>40</v>
@@ -36901,7 +36901,7 @@
         <v>2</v>
       </c>
       <c r="F1258" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1258">
         <v>80</v>
@@ -36930,7 +36930,7 @@
         <v>2</v>
       </c>
       <c r="F1259" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1259">
         <v>40</v>
@@ -36988,7 +36988,7 @@
         <v>2</v>
       </c>
       <c r="F1261" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1261">
         <v>80</v>
@@ -37017,7 +37017,7 @@
         <v>2</v>
       </c>
       <c r="F1262" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1262">
         <v>40</v>
@@ -37075,7 +37075,7 @@
         <v>2</v>
       </c>
       <c r="F1264" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1264">
         <v>80</v>
@@ -37104,7 +37104,7 @@
         <v>2</v>
       </c>
       <c r="F1265" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1265">
         <v>40</v>
@@ -37162,7 +37162,7 @@
         <v>2</v>
       </c>
       <c r="F1267" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1267">
         <v>80</v>
@@ -37191,7 +37191,7 @@
         <v>2</v>
       </c>
       <c r="F1268" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1268">
         <v>30</v>
@@ -37249,7 +37249,7 @@
         <v>2</v>
       </c>
       <c r="F1270" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1270">
         <v>90</v>
@@ -37278,7 +37278,7 @@
         <v>2</v>
       </c>
       <c r="F1271" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1271">
         <v>40</v>
@@ -37336,7 +37336,7 @@
         <v>2</v>
       </c>
       <c r="F1273" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1273">
         <v>100</v>
@@ -37365,7 +37365,7 @@
         <v>2</v>
       </c>
       <c r="F1274" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1274">
         <v>30</v>
@@ -37423,7 +37423,7 @@
         <v>2</v>
       </c>
       <c r="F1276" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1276">
         <v>90</v>
@@ -37452,7 +37452,7 @@
         <v>2</v>
       </c>
       <c r="F1277" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1277">
         <v>20</v>
@@ -37510,7 +37510,7 @@
         <v>2</v>
       </c>
       <c r="F1279" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1279">
         <v>80</v>
@@ -37539,7 +37539,7 @@
         <v>2</v>
       </c>
       <c r="F1280" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1280">
         <v>40</v>
@@ -37597,7 +37597,7 @@
         <v>2</v>
       </c>
       <c r="F1282" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1282">
         <v>100</v>
@@ -37626,7 +37626,7 @@
         <v>2</v>
       </c>
       <c r="F1283" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1283">
         <v>40</v>
@@ -37684,7 +37684,7 @@
         <v>2</v>
       </c>
       <c r="F1285" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1285">
         <v>100</v>
@@ -37713,7 +37713,7 @@
         <v>2</v>
       </c>
       <c r="F1286" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1286">
         <v>40</v>
@@ -37771,7 +37771,7 @@
         <v>2</v>
       </c>
       <c r="F1288" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1288">
         <v>100</v>
@@ -37800,7 +37800,7 @@
         <v>2</v>
       </c>
       <c r="F1289" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1289">
         <v>30</v>
@@ -37858,7 +37858,7 @@
         <v>2</v>
       </c>
       <c r="F1291" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1291">
         <v>90</v>
@@ -37887,7 +37887,7 @@
         <v>2</v>
       </c>
       <c r="F1292" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1292">
         <v>50</v>
@@ -37945,7 +37945,7 @@
         <v>2</v>
       </c>
       <c r="F1294" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1294">
         <v>110</v>
@@ -37974,7 +37974,7 @@
         <v>2</v>
       </c>
       <c r="F1295" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1295">
         <v>40</v>
@@ -38032,7 +38032,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1297">
         <v>100</v>
@@ -38061,7 +38061,7 @@
         <v>2</v>
       </c>
       <c r="F1298" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1298">
         <v>50</v>
@@ -38119,7 +38119,7 @@
         <v>2</v>
       </c>
       <c r="F1300" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1300">
         <v>110</v>
@@ -38148,7 +38148,7 @@
         <v>2</v>
       </c>
       <c r="F1301" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1301">
         <v>40</v>
@@ -38206,7 +38206,7 @@
         <v>2</v>
       </c>
       <c r="F1303" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1303">
         <v>100</v>
@@ -38235,7 +38235,7 @@
         <v>2</v>
       </c>
       <c r="F1304" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1304">
         <v>50</v>
@@ -38293,7 +38293,7 @@
         <v>2</v>
       </c>
       <c r="F1306" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1306">
         <v>110</v>
@@ -38322,7 +38322,7 @@
         <v>2</v>
       </c>
       <c r="F1307" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1307">
         <v>50</v>
@@ -38380,7 +38380,7 @@
         <v>2</v>
       </c>
       <c r="F1309" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1309">
         <v>110</v>
@@ -38409,7 +38409,7 @@
         <v>2</v>
       </c>
       <c r="F1310" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1310">
         <v>50</v>
@@ -38467,7 +38467,7 @@
         <v>2</v>
       </c>
       <c r="F1312" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1312">
         <v>110</v>
@@ -38496,7 +38496,7 @@
         <v>2</v>
       </c>
       <c r="F1313" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1313">
         <v>50</v>
@@ -38554,7 +38554,7 @@
         <v>2</v>
       </c>
       <c r="F1315" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1315">
         <v>110</v>
